--- a/03_Outputs/Turistica_Agroecologica/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/08_Educacion/educacion.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -37,23 +37,67 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -86,6 +130,14 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,15 +463,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="78.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="79.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
     <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
@@ -691,37 +743,35 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E9" s="5">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
         <v>2011</v>
       </c>
-      <c r="F9" s="7">
-        <v>0.919666742979243</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0.0378760302197802</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0.0180596306471306</v>
+      <c r="F9" s="6">
+        <v>0.846</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.0475</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.0325</v>
       </c>
     </row>
     <row r="10">
@@ -732,30 +782,30 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OCCIDENTE</t>
+          <t/>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
       <c r="E10" s="5">
         <v>2011</v>
       </c>
       <c r="F10" s="7">
-        <v>0.910143056346603</v>
+        <v>0.896628258247233</v>
       </c>
       <c r="G10" s="9">
-        <v>0.0455799831097669</v>
+        <v>0.0408858236744113</v>
       </c>
       <c r="H10" s="11">
-        <v>0.0166634169334407</v>
+        <v>0.0225757014737505</v>
       </c>
     </row>
     <row r="11">
@@ -766,71 +816,73 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>OCCIDENTE</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+          <t/>
         </is>
       </c>
       <c r="E11" s="5">
         <v>2011</v>
       </c>
       <c r="F11" s="7">
+        <v>0.910143056346603</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.0455799831097669</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0.0166634169334407</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E12" s="5">
+        <v>2011</v>
+      </c>
+      <c r="F12" s="7">
         <v>0.937766912719297</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G12" s="9">
         <v>0.0386950341647785</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H12" s="11">
         <v>0.0272899343592948</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>5113</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Buriticá</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E12" s="4">
-        <v>2012</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1.002</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.0406</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0.0054</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>5240</v>
+        <v>5113</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -847,22 +899,22 @@
         <v>2012</v>
       </c>
       <c r="F13" s="6">
-        <v>0.859</v>
+        <v>1.002</v>
       </c>
       <c r="G13" s="8">
-        <v>0.0285</v>
+        <v>0.0406</v>
       </c>
       <c r="H13" s="10">
-        <v>0.0027</v>
+        <v>0.0054</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>5306</v>
+        <v>5240</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -879,22 +931,22 @@
         <v>2012</v>
       </c>
       <c r="F14" s="6">
-        <v>1.072</v>
+        <v>0.859</v>
       </c>
       <c r="G14" s="8">
-        <v>0.0247</v>
+        <v>0.0285</v>
       </c>
       <c r="H14" s="10">
-        <v>0.0111</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>5347</v>
+        <v>5306</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -911,22 +963,22 @@
         <v>2012</v>
       </c>
       <c r="F15" s="6">
-        <v>0.87</v>
+        <v>1.072</v>
       </c>
       <c r="G15" s="8">
-        <v>0.0606</v>
+        <v>0.0247</v>
       </c>
       <c r="H15" s="10">
-        <v>0.0008</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>5501</v>
+        <v>5347</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -943,22 +995,22 @@
         <v>2012</v>
       </c>
       <c r="F16" s="6">
-        <v>0.809</v>
+        <v>0.87</v>
       </c>
       <c r="G16" s="8">
-        <v>0.0222</v>
+        <v>0.0606</v>
       </c>
       <c r="H16" s="10">
-        <v>0.0478</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>5628</v>
+        <v>5501</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -975,22 +1027,22 @@
         <v>2012</v>
       </c>
       <c r="F17" s="6">
-        <v>0.881</v>
+        <v>0.809</v>
       </c>
       <c r="G17" s="8">
-        <v>0.0331</v>
+        <v>0.0222</v>
       </c>
       <c r="H17" s="10">
-        <v>0.0194</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>5656</v>
+        <v>5628</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1007,81 +1059,77 @@
         <v>2012</v>
       </c>
       <c r="F18" s="6">
+        <v>0.881</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.0331</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0.0194</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>5656</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E19" s="4">
+        <v>2012</v>
+      </c>
+      <c r="F19" s="6">
         <v>0.941</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G19" s="8">
         <v>0.0441</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H19" s="10">
         <v>0.0066</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E19" s="5">
+    <row r="20">
+      <c r="A20">
+        <v>5042</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E20" s="4">
         <v>2012</v>
       </c>
-      <c r="F19" s="7">
-        <v>0.914187071116656</v>
-      </c>
-      <c r="G19" s="9">
-        <v>0.0372673112913288</v>
-      </c>
-      <c r="H19" s="11">
-        <v>0.010062515595758</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E20" s="5">
-        <v>2012</v>
-      </c>
-      <c r="F20" s="7">
-        <v>0.890220904848691</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0.0556864252668683</v>
-      </c>
-      <c r="H20" s="11">
-        <v>0.0115782259518135</v>
+      <c r="F20" s="6">
+        <v>0.888</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.0298</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0.0072</v>
       </c>
     </row>
     <row r="21">
@@ -1092,7 +1140,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1102,93 +1150,97 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
       <c r="E21" s="5">
         <v>2012</v>
       </c>
       <c r="F21" s="7">
+        <v>0.90600273399807</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0.0349335263214324</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.0091678835638469</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="5">
+        <v>2012</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.890220904848691</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0.0556864252668683</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.0115782259518135</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E23" s="5">
+        <v>2012</v>
+      </c>
+      <c r="F23" s="7">
         <v>0.925417166910917</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G23" s="9">
         <v>0.0386758823737154</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H23" s="11">
         <v>0.0206672371248529</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>5113</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Buriticá</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E22" s="4">
-        <v>2013</v>
-      </c>
-      <c r="F22" s="6">
-        <v>1.075</v>
-      </c>
-      <c r="G22" s="8">
-        <v>0.0356</v>
-      </c>
-      <c r="H22" s="10">
-        <v>0.0132</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>5240</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ebéjico</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E23" s="4">
-        <v>2013</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.817</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.0236</v>
-      </c>
-      <c r="H23" s="10">
-        <v>0.0016</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>5306</v>
+        <v>5113</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1205,22 +1257,22 @@
         <v>2013</v>
       </c>
       <c r="F24" s="6">
-        <v>1.154</v>
+        <v>1.075</v>
       </c>
       <c r="G24" s="8">
-        <v>0.0348</v>
+        <v>0.0356</v>
       </c>
       <c r="H24" s="10">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>5347</v>
+        <v>5240</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1237,22 +1289,22 @@
         <v>2013</v>
       </c>
       <c r="F25" s="6">
-        <v>0.819</v>
+        <v>0.817</v>
       </c>
       <c r="G25" s="8">
-        <v>0.0357</v>
+        <v>0.0236</v>
       </c>
       <c r="H25" s="10">
-        <v>0.0035</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>5501</v>
+        <v>5306</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1269,22 +1321,22 @@
         <v>2013</v>
       </c>
       <c r="F26" s="6">
-        <v>0.804</v>
+        <v>1.154</v>
       </c>
       <c r="G26" s="8">
-        <v>0.0238</v>
+        <v>0.0348</v>
       </c>
       <c r="H26" s="10">
-        <v>0.0327</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>5628</v>
+        <v>5347</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1301,22 +1353,22 @@
         <v>2013</v>
       </c>
       <c r="F27" s="6">
-        <v>0.912</v>
+        <v>0.819</v>
       </c>
       <c r="G27" s="8">
-        <v>0.0307</v>
+        <v>0.0357</v>
       </c>
       <c r="H27" s="10">
-        <v>0.0067</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>5656</v>
+        <v>5501</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1333,220 +1385,220 @@
         <v>2013</v>
       </c>
       <c r="F28" s="6">
+        <v>0.804</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.0238</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0.0327</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>5628</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E29" s="4">
+        <v>2013</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.912</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0.0307</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0.0067</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>5656</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E30" s="4">
+        <v>2013</v>
+      </c>
+      <c r="F30" s="6">
         <v>0.934</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G30" s="8">
         <v>0.0311</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H30" s="10">
         <v>0.0007</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31">
+        <v>5042</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E31" s="4">
+        <v>2013</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.922</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.0405</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E29" s="5">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E32" s="5">
         <v>2013</v>
       </c>
-      <c r="F29" s="7">
-        <v>0.91823782234957</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0.030288029290035</v>
-      </c>
-      <c r="H29" s="11">
-        <v>0.00684903693091372</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="F32" s="7">
+        <v>0.919423665994441</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.0335068567068186</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.0113094402354608</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E30" s="5">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E33" s="5">
         <v>2013</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F33" s="7">
         <v>0.896730947238507</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G33" s="9">
         <v>0.0331949562892111</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H33" s="11">
         <v>0.0149141149850869</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E31" s="5">
+      <c r="E34" s="5">
         <v>2013</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F34" s="7">
         <v>0.917079098894898</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G34" s="9">
         <v>0.0352980477155238</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H34" s="11">
         <v>0.0157495286288428</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>5113</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Buriticá</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E32" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0.8433</v>
-      </c>
-      <c r="G32" s="8">
-        <v>0.0457</v>
-      </c>
-      <c r="H32" s="10">
-        <v>0.0112</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>5240</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ebéjico</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E33" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0.8939</v>
-      </c>
-      <c r="G33" s="8">
-        <v>0.0137</v>
-      </c>
-      <c r="H33" s="10">
-        <v>0.0278</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>5306</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Giraldo</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E34" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0.9231</v>
-      </c>
-      <c r="G34" s="8">
-        <v>0.0369</v>
-      </c>
-      <c r="H34" s="10">
-        <v>0.0238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>5347</v>
+        <v>5113</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1563,22 +1615,22 @@
         <v>2014</v>
       </c>
       <c r="F35" s="6">
-        <v>0.9162</v>
+        <v>0.8433</v>
       </c>
       <c r="G35" s="8">
-        <v>0.019</v>
+        <v>0.0457</v>
       </c>
       <c r="H35" s="10">
-        <v>0.0038</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>5501</v>
+        <v>5240</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1595,22 +1647,22 @@
         <v>2014</v>
       </c>
       <c r="F36" s="6">
-        <v>0.9342</v>
+        <v>0.8939</v>
       </c>
       <c r="G36" s="8">
-        <v>0.0296</v>
+        <v>0.0137</v>
       </c>
       <c r="H36" s="10">
-        <v>0.0543</v>
+        <v>0.0278</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>5628</v>
+        <v>5306</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1627,22 +1679,22 @@
         <v>2014</v>
       </c>
       <c r="F37" s="6">
-        <v>0.8568</v>
+        <v>0.9231</v>
       </c>
       <c r="G37" s="8">
-        <v>0.0299</v>
+        <v>0.0369</v>
       </c>
       <c r="H37" s="10">
-        <v>0.0059</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>5656</v>
+        <v>5347</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1659,124 +1711,118 @@
         <v>2014</v>
       </c>
       <c r="F38" s="6">
+        <v>0.9162</v>
+      </c>
+      <c r="G38" s="8">
+        <v>0.019</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0.0038</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>5501</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E39" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0.9342</v>
+      </c>
+      <c r="G39" s="8">
+        <v>0.0296</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0.0543</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>5628</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E40" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0.8568</v>
+      </c>
+      <c r="G40" s="8">
+        <v>0.0299</v>
+      </c>
+      <c r="H40" s="10">
+        <v>0.0059</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>5656</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E41" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F41" s="6">
         <v>0.8724</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G41" s="8">
         <v>0.031</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H41" s="10">
         <v>0.0004</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E39" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F39" s="7">
-        <v>0.883335688244349</v>
-      </c>
-      <c r="G39" s="9">
-        <v>0.0278477274568581</v>
-      </c>
-      <c r="H39" s="11">
-        <v>0.0143394879688892</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E40" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F40" s="7">
-        <v>0.868804458170511</v>
-      </c>
-      <c r="G40" s="9">
-        <v>0.0266061809319719</v>
-      </c>
-      <c r="H40" s="11">
-        <v>0.0167604836337661</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E41" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F41" s="7">
-        <v>0.875394961441984</v>
-      </c>
-      <c r="G41" s="9">
-        <v>0.0230587570951566</v>
-      </c>
-      <c r="H41" s="11">
-        <v>0.0197792413069725</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>5113</v>
+        <v>5042</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1790,125 +1836,127 @@
         </is>
       </c>
       <c r="E42" s="4">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F42" s="6">
-        <v>1.1469</v>
+        <v>0.8626</v>
       </c>
       <c r="G42" s="8">
-        <v>0.0506</v>
+        <v>0.042</v>
       </c>
       <c r="H42" s="10">
-        <v>0.0027</v>
+        <v>0.0383</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>5240</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Ebéjico</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E43" s="4">
-        <v>2015</v>
-      </c>
-      <c r="F43" s="6">
-        <v>0.7644</v>
-      </c>
-      <c r="G43" s="8">
-        <v>0.0278</v>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E43" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F43" s="7">
+        <v>0.876778749099773</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0.0323228906985763</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.0219161653094011</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>5306</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Giraldo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E44" s="4">
-        <v>2015</v>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G44" s="8">
-        <v>0.066</v>
-      </c>
-      <c r="H44" s="10">
-        <v>0.0348</v>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E44" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F44" s="7">
+        <v>0.868804458170511</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0.0266061809319719</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0.0167604836337661</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>5347</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Heliconia</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E45" s="4">
-        <v>2015</v>
-      </c>
-      <c r="F45" s="6">
-        <v>0.7621</v>
-      </c>
-      <c r="G45" s="8">
-        <v>0.0467</v>
-      </c>
-      <c r="H45" s="10">
-        <v>0.0375</v>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E45" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F45" s="7">
+        <v>0.875394961441984</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0.0230587570951566</v>
+      </c>
+      <c r="H45" s="11">
+        <v>0.0197792413069725</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>5501</v>
+        <v>5113</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1925,24 +1973,22 @@
         <v>2015</v>
       </c>
       <c r="F46" s="6">
-        <v>0.7454</v>
+        <v>1.1469</v>
       </c>
       <c r="G46" s="8">
-        <v>0.0215</v>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>0.0506</v>
+      </c>
+      <c r="H46" s="10">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>5628</v>
+        <v>5240</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1959,10 +2005,10 @@
         <v>2015</v>
       </c>
       <c r="F47" s="6">
-        <v>0.8536</v>
+        <v>0.7644</v>
       </c>
       <c r="G47" s="8">
-        <v>0.065</v>
+        <v>0.0278</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
@@ -1972,11 +2018,11 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>5656</v>
+        <v>5306</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1992,125 +2038,125 @@
       <c r="E48" s="4">
         <v>2015</v>
       </c>
-      <c r="F48" s="6">
-        <v>0.9243</v>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G48" s="8">
-        <v>0.0354</v>
+        <v>0.066</v>
       </c>
       <c r="H48" s="10">
-        <v>0.0591</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E49" s="5">
+      <c r="A49">
+        <v>5347</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E49" s="4">
         <v>2015</v>
       </c>
-      <c r="F49" s="7">
-        <v>0.871303726100489</v>
-      </c>
-      <c r="G49" s="9">
-        <v>0.0434299843788539</v>
-      </c>
-      <c r="H49" s="11">
-        <v>0.0381759113001215</v>
+      <c r="F49" s="6">
+        <v>0.7621</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0.0467</v>
+      </c>
+      <c r="H49" s="10">
+        <v>0.0375</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E50" s="5">
+      <c r="A50">
+        <v>5501</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E50" s="4">
         <v>2015</v>
       </c>
-      <c r="F50" s="7">
-        <v>0.884824546527383</v>
-      </c>
-      <c r="G50" s="9">
-        <v>0.044422538349473</v>
-      </c>
-      <c r="H50" s="11">
-        <v>0.0217109540908915</v>
+      <c r="F50" s="6">
+        <v>0.7454</v>
+      </c>
+      <c r="G50" s="8">
+        <v>0.0215</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E51" s="5">
+      <c r="A51">
+        <v>5628</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E51" s="4">
         <v>2015</v>
       </c>
-      <c r="F51" s="7">
-        <v>0.896581626771714</v>
-      </c>
-      <c r="G51" s="9">
-        <v>0.0376652930788723</v>
-      </c>
-      <c r="H51" s="11">
-        <v>0.0270331317164015</v>
+      <c r="F51" s="6">
+        <v>0.8536</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0.065</v>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>5113</v>
+        <v>5656</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2124,25 +2170,25 @@
         </is>
       </c>
       <c r="E52" s="4">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F52" s="6">
-        <v>1.002</v>
+        <v>0.9243</v>
       </c>
       <c r="G52" s="8">
-        <v>0.0956</v>
+        <v>0.0354</v>
       </c>
       <c r="H52" s="10">
-        <v>0.0342</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>5240</v>
+        <v>5042</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2156,121 +2202,129 @@
         </is>
       </c>
       <c r="E53" s="4">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F53" s="6">
-        <v>0.7264</v>
+        <v>0.9363</v>
       </c>
       <c r="G53" s="8">
-        <v>0.0349</v>
-      </c>
-      <c r="H53" s="10">
-        <v>0.0301</v>
+        <v>0.0588</v>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>5306</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Giraldo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E54" s="4">
-        <v>2016</v>
-      </c>
-      <c r="F54" s="6">
-        <v>1.443</v>
-      </c>
-      <c r="G54" s="8">
-        <v>0.0607</v>
-      </c>
-      <c r="H54" s="10">
-        <v>0.0395</v>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E54" s="5">
+        <v>2015</v>
+      </c>
+      <c r="F54" s="7">
+        <v>0.893083165799432</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0.0483151149747616</v>
+      </c>
+      <c r="H54" s="11">
+        <v>0.0381759113001215</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <v>5347</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Heliconia</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E55" s="4">
-        <v>2016</v>
-      </c>
-      <c r="F55" s="6">
-        <v>0.7373</v>
-      </c>
-      <c r="G55" s="8">
-        <v>0.0332</v>
-      </c>
-      <c r="H55" s="10">
-        <v>0.0133</v>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E55" s="5">
+        <v>2015</v>
+      </c>
+      <c r="F55" s="7">
+        <v>0.884824546527383</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0.044422538349473</v>
+      </c>
+      <c r="H55" s="11">
+        <v>0.0217109540908915</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <v>5501</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Olaya</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E56" s="4">
-        <v>2016</v>
-      </c>
-      <c r="F56" s="6">
-        <v>0.745</v>
-      </c>
-      <c r="G56" s="8">
-        <v>0.0252</v>
-      </c>
-      <c r="H56" s="10">
-        <v>0.0285</v>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E56" s="5">
+        <v>2015</v>
+      </c>
+      <c r="F56" s="7">
+        <v>0.896581626771714</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0.0376652930788723</v>
+      </c>
+      <c r="H56" s="11">
+        <v>0.0270331317164015</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>5628</v>
+        <v>5113</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2287,22 +2341,22 @@
         <v>2016</v>
       </c>
       <c r="F57" s="6">
-        <v>0.8625</v>
+        <v>1.002</v>
       </c>
       <c r="G57" s="8">
-        <v>0.0726</v>
+        <v>0.0956</v>
       </c>
       <c r="H57" s="10">
-        <v>0.036</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>5656</v>
+        <v>5240</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2319,124 +2373,118 @@
         <v>2016</v>
       </c>
       <c r="F58" s="6">
-        <v>0.8508</v>
+        <v>0.7264</v>
       </c>
       <c r="G58" s="8">
-        <v>0.0321</v>
+        <v>0.0349</v>
       </c>
       <c r="H58" s="10">
-        <v>0.006</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E59" s="5">
+      <c r="A59">
+        <v>5306</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E59" s="4">
         <v>2016</v>
       </c>
-      <c r="F59" s="7">
-        <v>0.869169636635142</v>
-      </c>
-      <c r="G59" s="9">
-        <v>0.0495103202256512</v>
-      </c>
-      <c r="H59" s="11">
-        <v>0.0248350589016094</v>
+      <c r="F59" s="6">
+        <v>1.443</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0.0607</v>
+      </c>
+      <c r="H59" s="10">
+        <v>0.0395</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E60" s="5">
+      <c r="A60">
+        <v>5347</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E60" s="4">
         <v>2016</v>
       </c>
-      <c r="F60" s="7">
-        <v>0.892128532355048</v>
-      </c>
-      <c r="G60" s="9">
-        <v>0.0446758417088154</v>
-      </c>
-      <c r="H60" s="11">
-        <v>0.0201417326936853</v>
+      <c r="F60" s="6">
+        <v>0.7373</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0.0332</v>
+      </c>
+      <c r="H60" s="10">
+        <v>0.0133</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E61" s="5">
+      <c r="A61">
+        <v>5501</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E61" s="4">
         <v>2016</v>
       </c>
-      <c r="F61" s="7">
-        <v>0.880778160798706</v>
-      </c>
-      <c r="G61" s="9">
-        <v>0.0445068669490581</v>
-      </c>
-      <c r="H61" s="11">
-        <v>0.0303631515547205</v>
+      <c r="F61" s="6">
+        <v>0.745</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0.0252</v>
+      </c>
+      <c r="H61" s="10">
+        <v>0.0285</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>5113</v>
+        <v>5628</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2450,25 +2498,25 @@
         </is>
       </c>
       <c r="E62" s="4">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F62" s="6">
-        <v>0.9791</v>
+        <v>0.8625</v>
       </c>
       <c r="G62" s="8">
-        <v>0.041</v>
+        <v>0.0726</v>
       </c>
       <c r="H62" s="10">
-        <v>0.0476</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>5240</v>
+        <v>5656</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2482,25 +2530,25 @@
         </is>
       </c>
       <c r="E63" s="4">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F63" s="6">
-        <v>0.6772</v>
+        <v>0.8508</v>
       </c>
       <c r="G63" s="8">
-        <v>0.0454</v>
+        <v>0.0321</v>
       </c>
       <c r="H63" s="10">
-        <v>0.0979</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>5306</v>
+        <v>5042</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2514,121 +2562,127 @@
         </is>
       </c>
       <c r="E64" s="4">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F64" s="6">
-        <v>1.2522</v>
+        <v>1.0621</v>
       </c>
       <c r="G64" s="8">
-        <v>0.0052</v>
+        <v>0.0777</v>
       </c>
       <c r="H64" s="10">
-        <v>0.0017</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65">
-        <v>5347</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Heliconia</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E65" s="4">
-        <v>2017</v>
-      </c>
-      <c r="F65" s="6">
-        <v>0.7187</v>
-      </c>
-      <c r="G65" s="8">
-        <v>0.0697</v>
-      </c>
-      <c r="H65" s="10">
-        <v>0.0657</v>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E65" s="5">
+        <v>2016</v>
+      </c>
+      <c r="F65" s="7">
+        <v>0.930859446952596</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0.0585240180586907</v>
+      </c>
+      <c r="H65" s="11">
+        <v>0.0213065801354402</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66">
-        <v>5501</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Olaya</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E66" s="4">
-        <v>2017</v>
-      </c>
-      <c r="F66" s="6">
-        <v>0.692</v>
-      </c>
-      <c r="G66" s="8">
-        <v>0.0446</v>
-      </c>
-      <c r="H66" s="10">
-        <v>0.0927</v>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E66" s="5">
+        <v>2016</v>
+      </c>
+      <c r="F66" s="7">
+        <v>0.892128532355048</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0.0446758417088154</v>
+      </c>
+      <c r="H66" s="11">
+        <v>0.0201417326936853</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67">
-        <v>5628</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Sabanalarga</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E67" s="4">
-        <v>2017</v>
-      </c>
-      <c r="F67" s="6">
-        <v>0.8373</v>
-      </c>
-      <c r="G67" s="8">
-        <v>0.0727</v>
-      </c>
-      <c r="H67" s="10">
-        <v>0.0801</v>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E67" s="5">
+        <v>2016</v>
+      </c>
+      <c r="F67" s="7">
+        <v>0.880778160798706</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0.0445068669490581</v>
+      </c>
+      <c r="H67" s="11">
+        <v>0.0303631515547205</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>5656</v>
+        <v>5113</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,124 +2699,118 @@
         <v>2017</v>
       </c>
       <c r="F68" s="6">
-        <v>0.8263</v>
+        <v>0.9791</v>
       </c>
       <c r="G68" s="8">
-        <v>0.0336</v>
+        <v>0.041</v>
       </c>
       <c r="H68" s="10">
-        <v>0.025</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E69" s="5">
+      <c r="A69">
+        <v>5240</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E69" s="4">
         <v>2017</v>
       </c>
-      <c r="F69" s="7">
-        <v>0.825446841885691</v>
-      </c>
-      <c r="G69" s="9">
-        <v>0.0464209345014602</v>
-      </c>
-      <c r="H69" s="11">
-        <v>0.060641802252816</v>
+      <c r="F69" s="6">
+        <v>0.6772</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0.0454</v>
+      </c>
+      <c r="H69" s="10">
+        <v>0.0979</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E70" s="5">
+      <c r="A70">
+        <v>5306</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E70" s="4">
         <v>2017</v>
       </c>
-      <c r="F70" s="7">
-        <v>0.86341664655683</v>
-      </c>
-      <c r="G70" s="9">
-        <v>0.0457878331834236</v>
-      </c>
-      <c r="H70" s="11">
-        <v>0.0478882609744861</v>
+      <c r="F70" s="6">
+        <v>1.2522</v>
+      </c>
+      <c r="G70" s="8">
+        <v>0.0052</v>
+      </c>
+      <c r="H70" s="10">
+        <v>0.0017</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E71" s="5">
+      <c r="A71">
+        <v>5347</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E71" s="4">
         <v>2017</v>
       </c>
-      <c r="F71" s="7">
-        <v>0.860061148330256</v>
-      </c>
-      <c r="G71" s="9">
-        <v>0.0412962685762201</v>
-      </c>
-      <c r="H71" s="11">
-        <v>0.0629679217859941</v>
+      <c r="F71" s="6">
+        <v>0.7187</v>
+      </c>
+      <c r="G71" s="8">
+        <v>0.0697</v>
+      </c>
+      <c r="H71" s="10">
+        <v>0.0657</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>5113</v>
+        <v>5501</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2776,25 +2824,25 @@
         </is>
       </c>
       <c r="E72" s="4">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F72" s="6">
-        <v>0.7383</v>
+        <v>0.692</v>
       </c>
       <c r="G72" s="8">
-        <v>0.0525</v>
+        <v>0.0446</v>
       </c>
       <c r="H72" s="10">
-        <v>0.0219</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>5240</v>
+        <v>5628</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2808,25 +2856,25 @@
         </is>
       </c>
       <c r="E73" s="4">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F73" s="6">
-        <v>0.8305</v>
+        <v>0.8373</v>
       </c>
       <c r="G73" s="8">
-        <v>0.0274</v>
+        <v>0.0727</v>
       </c>
       <c r="H73" s="10">
-        <v>0.0208</v>
+        <v>0.0801</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>5306</v>
+        <v>5656</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2840,25 +2888,25 @@
         </is>
       </c>
       <c r="E74" s="4">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F74" s="6">
-        <v>0.932</v>
+        <v>0.8263</v>
       </c>
       <c r="G74" s="8">
-        <v>0.0344</v>
+        <v>0.0336</v>
       </c>
       <c r="H74" s="10">
-        <v>0.0215</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>5347</v>
+        <v>5042</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2872,223 +2920,223 @@
         </is>
       </c>
       <c r="E75" s="4">
+        <v>2017</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0.9896</v>
+      </c>
+      <c r="G75" s="8">
+        <v>0.0543</v>
+      </c>
+      <c r="H75" s="10">
+        <v>0.0242</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E76" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F76" s="7">
+        <v>0.878222305253623</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0.0489540647644928</v>
+      </c>
+      <c r="H76" s="11">
+        <v>0.0489257133152174</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E77" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F77" s="7">
+        <v>0.86341664655683</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0.0457878331834236</v>
+      </c>
+      <c r="H77" s="11">
+        <v>0.0478882609744861</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E78" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F78" s="7">
+        <v>0.860061148330256</v>
+      </c>
+      <c r="G78" s="9">
+        <v>0.0412962685762201</v>
+      </c>
+      <c r="H78" s="11">
+        <v>0.0629679217859941</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>5113</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E79" s="4">
         <v>2018</v>
       </c>
-      <c r="F75" s="6">
-        <v>0.9734</v>
-      </c>
-      <c r="G75" s="8">
-        <v>0.0374</v>
-      </c>
-      <c r="H75" s="10">
-        <v>0.047</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>5501</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Olaya</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E76" s="4">
+      <c r="F79" s="6">
+        <v>0.7383</v>
+      </c>
+      <c r="G79" s="8">
+        <v>0.0525</v>
+      </c>
+      <c r="H79" s="10">
+        <v>0.0219</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5240</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E80" s="4">
         <v>2018</v>
       </c>
-      <c r="F76" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="G76" s="8">
-        <v>0.0401</v>
-      </c>
-      <c r="H76" s="10">
-        <v>0.063</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>5628</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Sabanalarga</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E77" s="4">
+      <c r="F80" s="6">
+        <v>0.8305</v>
+      </c>
+      <c r="G80" s="8">
+        <v>0.0274</v>
+      </c>
+      <c r="H80" s="10">
+        <v>0.0208</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5306</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E81" s="4">
         <v>2018</v>
       </c>
-      <c r="F77" s="6">
-        <v>0.8127</v>
-      </c>
-      <c r="G77" s="8">
-        <v>0.0471</v>
-      </c>
-      <c r="H77" s="10">
-        <v>0.0739</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>5656</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>San Jerónimo</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E78" s="4">
-        <v>2018</v>
-      </c>
-      <c r="F78" s="6">
-        <v>0.7782</v>
-      </c>
-      <c r="G78" s="8">
-        <v>0.0238</v>
-      </c>
-      <c r="H78" s="10">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E79" s="5">
-        <v>2018</v>
-      </c>
-      <c r="F79" s="7">
-        <v>0.818121912822683</v>
-      </c>
-      <c r="G79" s="9">
-        <v>0.0365884638171815</v>
-      </c>
-      <c r="H79" s="11">
-        <v>0.0297037325433771</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E80" s="5">
-        <v>2018</v>
-      </c>
-      <c r="F80" s="7">
-        <v>0.867536816256646</v>
-      </c>
-      <c r="G80" s="9">
-        <v>0.034466941515725</v>
-      </c>
-      <c r="H80" s="11">
-        <v>0.0336020974137154</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E81" s="5">
-        <v>2018</v>
-      </c>
-      <c r="F81" s="7">
-        <v>0.941091334421984</v>
-      </c>
-      <c r="G81" s="9">
-        <v>0.039030509551254</v>
-      </c>
-      <c r="H81" s="11">
-        <v>0.0314218356950779</v>
+      <c r="F81" s="6">
+        <v>0.932</v>
+      </c>
+      <c r="G81" s="8">
+        <v>0.0344</v>
+      </c>
+      <c r="H81" s="10">
+        <v>0.0215</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>5113</v>
+        <v>5347</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3102,25 +3150,25 @@
         </is>
       </c>
       <c r="E82" s="4">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F82" s="6">
-        <v>0.7667</v>
+        <v>0.9734</v>
       </c>
       <c r="G82" s="8">
-        <v>0.0421</v>
+        <v>0.0374</v>
       </c>
       <c r="H82" s="10">
-        <v>0.0181</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>5240</v>
+        <v>5501</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3134,25 +3182,25 @@
         </is>
       </c>
       <c r="E83" s="4">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F83" s="6">
-        <v>0.8077</v>
+        <v>0.8</v>
       </c>
       <c r="G83" s="8">
-        <v>0.04</v>
+        <v>0.0401</v>
       </c>
       <c r="H83" s="10">
-        <v>0.0203</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>5306</v>
+        <v>5628</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3166,25 +3214,25 @@
         </is>
       </c>
       <c r="E84" s="4">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F84" s="6">
-        <v>0.9465</v>
+        <v>0.8127</v>
       </c>
       <c r="G84" s="8">
-        <v>0.0526</v>
+        <v>0.0471</v>
       </c>
       <c r="H84" s="10">
-        <v>0.0075</v>
+        <v>0.0739</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>5347</v>
+        <v>5656</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3198,25 +3246,25 @@
         </is>
       </c>
       <c r="E85" s="4">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F85" s="6">
-        <v>0.9818</v>
+        <v>0.7782</v>
       </c>
       <c r="G85" s="8">
-        <v>0.0517</v>
+        <v>0.0238</v>
       </c>
       <c r="H85" s="10">
-        <v>0.0215</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>5501</v>
+        <v>5042</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3230,80 +3278,84 @@
         </is>
       </c>
       <c r="E86" s="4">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F86" s="6">
-        <v>0.7516</v>
+        <v>1.0545</v>
       </c>
       <c r="G86" s="8">
-        <v>0.0287</v>
+        <v>0.0464</v>
       </c>
       <c r="H86" s="10">
-        <v>0.0739</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <v>5628</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Sabanalarga</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E87" s="4">
-        <v>2019</v>
-      </c>
-      <c r="F87" s="6">
-        <v>0.7889</v>
-      </c>
-      <c r="G87" s="8">
-        <v>0.0454</v>
-      </c>
-      <c r="H87" s="10">
-        <v>0.0262</v>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E87" s="5">
+        <v>2018</v>
+      </c>
+      <c r="F87" s="7">
+        <v>0.889917107666922</v>
+      </c>
+      <c r="G87" s="9">
+        <v>0.039568524957275</v>
+      </c>
+      <c r="H87" s="11">
+        <v>0.0250858978136602</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88">
-        <v>5656</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>San Jerónimo</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E88" s="4">
-        <v>2019</v>
-      </c>
-      <c r="F88" s="6">
-        <v>0.8049</v>
-      </c>
-      <c r="G88" s="8">
-        <v>0.0119</v>
-      </c>
-      <c r="H88" s="10">
-        <v>0.0365</v>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E88" s="5">
+        <v>2018</v>
+      </c>
+      <c r="F88" s="7">
+        <v>0.867536816256646</v>
+      </c>
+      <c r="G88" s="9">
+        <v>0.034466941515725</v>
+      </c>
+      <c r="H88" s="11">
+        <v>0.0336020974137154</v>
       </c>
     </row>
     <row r="89">
@@ -3314,7 +3366,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3324,97 +3376,93 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
       <c r="E89" s="5">
+        <v>2018</v>
+      </c>
+      <c r="F89" s="7">
+        <v>0.941091334421984</v>
+      </c>
+      <c r="G89" s="9">
+        <v>0.039030509551254</v>
+      </c>
+      <c r="H89" s="11">
+        <v>0.0314218356950779</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>5113</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E90" s="4">
         <v>2019</v>
       </c>
-      <c r="F89" s="7">
-        <v>0.820866058609915</v>
-      </c>
-      <c r="G89" s="9">
-        <v>0.0360527066970695</v>
-      </c>
-      <c r="H89" s="11">
-        <v>0.026432961743096</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E90" s="5">
+      <c r="F90" s="6">
+        <v>0.7667</v>
+      </c>
+      <c r="G90" s="8">
+        <v>0.0421</v>
+      </c>
+      <c r="H90" s="10">
+        <v>0.0181</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5240</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E91" s="4">
         <v>2019</v>
       </c>
-      <c r="F90" s="7">
-        <v>0.85901333709641</v>
-      </c>
-      <c r="G90" s="9">
-        <v>0.0381954007676676</v>
-      </c>
-      <c r="H90" s="11">
-        <v>0.031516367125762</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E91" s="5">
-        <v>2019</v>
-      </c>
-      <c r="F91" s="7">
-        <v>0.938328027409053</v>
-      </c>
-      <c r="G91" s="9">
-        <v>0.0399836572650948</v>
-      </c>
-      <c r="H91" s="11">
-        <v>0.0321797918233716</v>
+      <c r="F91" s="6">
+        <v>0.8077</v>
+      </c>
+      <c r="G91" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="H91" s="10">
+        <v>0.0203</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>5113</v>
+        <v>5306</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3428,25 +3476,25 @@
         </is>
       </c>
       <c r="E92" s="4">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F92" s="6">
-        <v>0.7848</v>
+        <v>0.9465</v>
       </c>
       <c r="G92" s="8">
-        <v>0.0366</v>
+        <v>0.0526</v>
       </c>
       <c r="H92" s="10">
-        <v>0.061</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>5240</v>
+        <v>5347</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3460,25 +3508,25 @@
         </is>
       </c>
       <c r="E93" s="4">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F93" s="6">
-        <v>0.7552</v>
+        <v>0.9818</v>
       </c>
       <c r="G93" s="8">
-        <v>0.0148</v>
+        <v>0.0517</v>
       </c>
       <c r="H93" s="10">
-        <v>0.0815</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>5306</v>
+        <v>5501</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3492,25 +3540,25 @@
         </is>
       </c>
       <c r="E94" s="4">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F94" s="6">
-        <v>0.9324</v>
+        <v>0.7516</v>
       </c>
       <c r="G94" s="8">
-        <v>0.0465</v>
+        <v>0.0287</v>
       </c>
       <c r="H94" s="10">
-        <v>0.0745</v>
+        <v>0.0739</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>5347</v>
+        <v>5628</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3524,25 +3572,25 @@
         </is>
       </c>
       <c r="E95" s="4">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F95" s="6">
-        <v>0.9378</v>
+        <v>0.7889</v>
       </c>
       <c r="G95" s="8">
-        <v>0.0288</v>
+        <v>0.0454</v>
       </c>
       <c r="H95" s="10">
-        <v>0.0704</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>5501</v>
+        <v>5656</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3556,25 +3604,25 @@
         </is>
       </c>
       <c r="E96" s="4">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F96" s="6">
-        <v>0.7758</v>
+        <v>0.8049</v>
       </c>
       <c r="G96" s="8">
-        <v>0.0117</v>
+        <v>0.0119</v>
       </c>
       <c r="H96" s="10">
-        <v>0.0352</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>5628</v>
+        <v>5042</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3588,48 +3636,50 @@
         </is>
       </c>
       <c r="E97" s="4">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F97" s="6">
-        <v>0.7784</v>
+        <v>0.9969</v>
       </c>
       <c r="G97" s="8">
-        <v>0.0041</v>
+        <v>0.0608</v>
       </c>
       <c r="H97" s="10">
-        <v>0.0738</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98">
-        <v>5656</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>San Jerónimo</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E98" s="4">
-        <v>2020</v>
-      </c>
-      <c r="F98" s="6">
-        <v>0.8424</v>
-      </c>
-      <c r="G98" s="8">
-        <v>0.0333</v>
-      </c>
-      <c r="H98" s="10">
-        <v>0.0449</v>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E98" s="5">
+        <v>2019</v>
+      </c>
+      <c r="F98" s="7">
+        <v>0.874171673339614</v>
+      </c>
+      <c r="G98" s="9">
+        <v>0.043546543805935</v>
+      </c>
+      <c r="H98" s="11">
+        <v>0.0269074835138954</v>
       </c>
     </row>
     <row r="99">
@@ -3640,30 +3690,30 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>OCCIDENTE</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+          <t/>
         </is>
       </c>
       <c r="E99" s="5">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F99" s="7">
-        <v>0.819000589523328</v>
+        <v>0.85901333709641</v>
       </c>
       <c r="G99" s="9">
-        <v>0.0255658244904834</v>
+        <v>0.0381954007676676</v>
       </c>
       <c r="H99" s="11">
-        <v>0.0635274296782887</v>
+        <v>0.031516367125762</v>
       </c>
     </row>
     <row r="100">
@@ -3674,73 +3724,71 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>OCCIDENTE</t>
+          <t/>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
       <c r="E100" s="5">
+        <v>2019</v>
+      </c>
+      <c r="F100" s="7">
+        <v>0.938328027409053</v>
+      </c>
+      <c r="G100" s="9">
+        <v>0.0399836572650948</v>
+      </c>
+      <c r="H100" s="11">
+        <v>0.0321797918233716</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>5113</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E101" s="4">
         <v>2020</v>
       </c>
-      <c r="F100" s="7">
-        <v>0.849113688178596</v>
-      </c>
-      <c r="G100" s="9">
-        <v>0.0222978081758877</v>
-      </c>
-      <c r="H100" s="11">
-        <v>0.067142114173495</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E101" s="5">
-        <v>2020</v>
-      </c>
-      <c r="F101" s="7">
-        <v>0.934267148996351</v>
-      </c>
-      <c r="G101" s="9">
-        <v>0.0230040799236241</v>
-      </c>
-      <c r="H101" s="11">
-        <v>0.0651083850135821</v>
+      <c r="F101" s="6">
+        <v>0.7848</v>
+      </c>
+      <c r="G101" s="8">
+        <v>0.0366</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.061</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>5113</v>
+        <v>5240</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3754,25 +3802,25 @@
         </is>
       </c>
       <c r="E102" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F102" s="6">
-        <v>0.7774</v>
+        <v>0.7552</v>
       </c>
       <c r="G102" s="8">
-        <v>0.0841</v>
+        <v>0.0148</v>
       </c>
       <c r="H102" s="10">
-        <v>0.1048</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>5240</v>
+        <v>5306</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3786,25 +3834,25 @@
         </is>
       </c>
       <c r="E103" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F103" s="6">
-        <v>0.7749</v>
+        <v>0.9324</v>
       </c>
       <c r="G103" s="8">
-        <v>0.0543</v>
+        <v>0.0465</v>
       </c>
       <c r="H103" s="10">
-        <v>0.1032</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>5306</v>
+        <v>5347</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3818,25 +3866,25 @@
         </is>
       </c>
       <c r="E104" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F104" s="6">
-        <v>0.9808</v>
+        <v>0.9378</v>
       </c>
       <c r="G104" s="8">
-        <v>0.0461</v>
+        <v>0.0288</v>
       </c>
       <c r="H104" s="10">
-        <v>0.0828</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>5347</v>
+        <v>5501</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3850,25 +3898,25 @@
         </is>
       </c>
       <c r="E105" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F105" s="6">
-        <v>0.9264</v>
+        <v>0.7758</v>
       </c>
       <c r="G105" s="8">
-        <v>0.059</v>
+        <v>0.0117</v>
       </c>
       <c r="H105" s="10">
-        <v>0.0408</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>5501</v>
+        <v>5628</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3882,25 +3930,25 @@
         </is>
       </c>
       <c r="E106" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F106" s="6">
-        <v>0.754</v>
+        <v>0.7784</v>
       </c>
       <c r="G106" s="8">
-        <v>0.0522</v>
+        <v>0.0041</v>
       </c>
       <c r="H106" s="10">
-        <v>0.0382</v>
+        <v>0.0738</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>5628</v>
+        <v>5656</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3914,25 +3962,25 @@
         </is>
       </c>
       <c r="E107" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F107" s="6">
-        <v>0.7831</v>
+        <v>0.8424</v>
       </c>
       <c r="G107" s="8">
-        <v>0.0539</v>
+        <v>0.0333</v>
       </c>
       <c r="H107" s="10">
-        <v>0.0701</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>5656</v>
+        <v>5042</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3946,16 +3994,16 @@
         </is>
       </c>
       <c r="E108" s="4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F108" s="6">
-        <v>0.8373</v>
+        <v>0.9119</v>
       </c>
       <c r="G108" s="8">
-        <v>0.0711</v>
+        <v>0.0186</v>
       </c>
       <c r="H108" s="10">
-        <v>0.0839</v>
+        <v>0.0846</v>
       </c>
     </row>
     <row r="109">
@@ -3980,16 +4028,16 @@
         </is>
       </c>
       <c r="E109" s="5">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F109" s="7">
-        <v>0.805241335482816</v>
+        <v>0.847039201505263</v>
       </c>
       <c r="G109" s="9">
-        <v>0.0650883320483166</v>
+        <v>0.023463420944317</v>
       </c>
       <c r="H109" s="11">
-        <v>0.0828765215765987</v>
+        <v>0.069887487505145</v>
       </c>
     </row>
     <row r="110">
@@ -4014,16 +4062,16 @@
         </is>
       </c>
       <c r="E110" s="5">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F110" s="7">
-        <v>0.839551588466629</v>
+        <v>0.849113688178596</v>
       </c>
       <c r="G110" s="9">
-        <v>0.0579854236957749</v>
+        <v>0.0222978081758877</v>
       </c>
       <c r="H110" s="11">
-        <v>0.0699376159957595</v>
+        <v>0.067142114173495</v>
       </c>
     </row>
     <row r="111">
@@ -4048,16 +4096,16 @@
         </is>
       </c>
       <c r="E111" s="5">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F111" s="7">
-        <v>0.924418856993982</v>
+        <v>0.934267148996351</v>
       </c>
       <c r="G111" s="9">
-        <v>0.0471531226376282</v>
+        <v>0.0230040799236241</v>
       </c>
       <c r="H111" s="11">
-        <v>0.0582136438740334</v>
+        <v>0.0651083850135821</v>
       </c>
     </row>
     <row r="112">
@@ -4080,16 +4128,16 @@
         </is>
       </c>
       <c r="E112" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F112" s="6">
-        <v>0.8057</v>
+        <v>0.7774</v>
       </c>
       <c r="G112" s="8">
-        <v>0.0778</v>
+        <v>0.0841</v>
       </c>
       <c r="H112" s="10">
-        <v>0.1124</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="113">
@@ -4112,16 +4160,16 @@
         </is>
       </c>
       <c r="E113" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F113" s="6">
-        <v>0.7554</v>
+        <v>0.7749</v>
       </c>
       <c r="G113" s="8">
-        <v>0.0425</v>
+        <v>0.0543</v>
       </c>
       <c r="H113" s="10">
-        <v>0.0622</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="114">
@@ -4144,16 +4192,16 @@
         </is>
       </c>
       <c r="E114" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F114" s="6">
-        <v>1.028</v>
+        <v>0.9808</v>
       </c>
       <c r="G114" s="8">
-        <v>0.0699</v>
+        <v>0.0461</v>
       </c>
       <c r="H114" s="10">
-        <v>0.1304</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="115">
@@ -4176,16 +4224,16 @@
         </is>
       </c>
       <c r="E115" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F115" s="6">
-        <v>0.8643</v>
+        <v>0.9264</v>
       </c>
       <c r="G115" s="8">
-        <v>0.0527</v>
+        <v>0.059</v>
       </c>
       <c r="H115" s="10">
-        <v>0.0674</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="116">
@@ -4208,16 +4256,16 @@
         </is>
       </c>
       <c r="E116" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F116" s="6">
-        <v>0.7466</v>
+        <v>0.754</v>
       </c>
       <c r="G116" s="8">
-        <v>0.0229</v>
+        <v>0.0522</v>
       </c>
       <c r="H116" s="10">
-        <v>0.1417</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="117">
@@ -4240,16 +4288,16 @@
         </is>
       </c>
       <c r="E117" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F117" s="6">
-        <v>0.7933</v>
+        <v>0.7831</v>
       </c>
       <c r="G117" s="8">
-        <v>0.018</v>
+        <v>0.0539</v>
       </c>
       <c r="H117" s="10">
-        <v>0.0832</v>
+        <v>0.0701</v>
       </c>
     </row>
     <row r="118">
@@ -4272,50 +4320,48 @@
         </is>
       </c>
       <c r="E118" s="4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F118" s="6">
-        <v>0.8564</v>
+        <v>0.8373</v>
       </c>
       <c r="G118" s="8">
-        <v>0.0264</v>
+        <v>0.0711</v>
       </c>
       <c r="H118" s="10">
-        <v>0.085</v>
+        <v>0.0839</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E119" s="5">
-        <v>2022</v>
-      </c>
-      <c r="F119" s="7">
-        <v>0.832019556016239</v>
-      </c>
-      <c r="G119" s="9">
-        <v>0.0432288589444588</v>
-      </c>
-      <c r="H119" s="11">
-        <v>0.0921392070484582</v>
+      <c r="A119">
+        <v>5042</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E119" s="4">
+        <v>2021</v>
+      </c>
+      <c r="F119" s="6">
+        <v>0.9291</v>
+      </c>
+      <c r="G119" s="8">
+        <v>0.0592</v>
+      </c>
+      <c r="H119" s="10">
+        <v>0.0862</v>
       </c>
     </row>
     <row r="120">
@@ -4326,30 +4372,30 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>OCCIDENTE</t>
+          <t/>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
       </c>
       <c r="E120" s="5">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F120" s="7">
-        <v>0.853651854751433</v>
+        <v>0.845389935100823</v>
       </c>
       <c r="G120" s="9">
-        <v>0.0414737755877409</v>
+        <v>0.0631796380805002</v>
       </c>
       <c r="H120" s="11">
-        <v>0.0844889083331414</v>
+        <v>0.0839538221036176</v>
       </c>
     </row>
     <row r="121">
@@ -4360,71 +4406,73 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E121" s="5">
+        <v>2021</v>
+      </c>
+      <c r="F121" s="7">
+        <v>0.839551588466629</v>
+      </c>
+      <c r="G121" s="9">
+        <v>0.0579854236957749</v>
+      </c>
+      <c r="H121" s="11">
+        <v>0.0699376159957595</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E121" s="5">
-        <v>2022</v>
-      </c>
-      <c r="F121" s="7">
-        <v>0.933206334367635</v>
-      </c>
-      <c r="G121" s="9">
-        <v>0.0470407053528837</v>
-      </c>
-      <c r="H121" s="11">
-        <v>0.0650811900901068</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122">
-        <v>5113</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Buriticá</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E122" s="4">
-        <v>2023</v>
-      </c>
-      <c r="F122" s="6">
-        <v>0.8024</v>
-      </c>
-      <c r="G122" s="8">
-        <v>0.0689</v>
-      </c>
-      <c r="H122" s="10">
-        <v>0.1224</v>
+      <c r="E122" s="5">
+        <v>2021</v>
+      </c>
+      <c r="F122" s="7">
+        <v>0.924418856993982</v>
+      </c>
+      <c r="G122" s="9">
+        <v>0.0471531226376282</v>
+      </c>
+      <c r="H122" s="11">
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>5240</v>
+        <v>5113</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4438,25 +4486,25 @@
         </is>
       </c>
       <c r="E123" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F123" s="6">
-        <v>0.6982</v>
+        <v>0.8057</v>
       </c>
       <c r="G123" s="8">
-        <v>0.0534</v>
+        <v>0.0778</v>
       </c>
       <c r="H123" s="10">
-        <v>0.1129</v>
+        <v>0.1124</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>5306</v>
+        <v>5240</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4470,25 +4518,25 @@
         </is>
       </c>
       <c r="E124" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F124" s="6">
-        <v>1.0116</v>
+        <v>0.7554</v>
       </c>
       <c r="G124" s="8">
-        <v>0.0483</v>
+        <v>0.0425</v>
       </c>
       <c r="H124" s="10">
-        <v>0.1379</v>
+        <v>0.0622</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>5347</v>
+        <v>5306</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4502,25 +4550,25 @@
         </is>
       </c>
       <c r="E125" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F125" s="6">
-        <v>0.7902</v>
+        <v>1.028</v>
       </c>
       <c r="G125" s="8">
-        <v>0.0734</v>
+        <v>0.0699</v>
       </c>
       <c r="H125" s="10">
-        <v>0.1272</v>
+        <v>0.1304</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>5501</v>
+        <v>5347</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4534,25 +4582,25 @@
         </is>
       </c>
       <c r="E126" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F126" s="6">
-        <v>0.8116</v>
+        <v>0.8643</v>
       </c>
       <c r="G126" s="8">
-        <v>0.0352</v>
+        <v>0.0527</v>
       </c>
       <c r="H126" s="10">
-        <v>0.0938</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>5628</v>
+        <v>5501</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Olaya</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4566,116 +4614,112 @@
         </is>
       </c>
       <c r="E127" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F127" s="6">
-        <v>0.7857</v>
+        <v>0.7466</v>
       </c>
       <c r="G127" s="8">
-        <v>0.045</v>
+        <v>0.0229</v>
       </c>
       <c r="H127" s="10">
-        <v>0.0911</v>
+        <v>0.1417</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
+        <v>5628</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E128" s="4">
+        <v>2022</v>
+      </c>
+      <c r="F128" s="6">
+        <v>0.7933</v>
+      </c>
+      <c r="G128" s="8">
+        <v>0.018</v>
+      </c>
+      <c r="H128" s="10">
+        <v>0.0832</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
         <v>5656</v>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>San Jerónimo</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E128" s="4">
-        <v>2023</v>
-      </c>
-      <c r="F128" s="6">
-        <v>0.848</v>
-      </c>
-      <c r="G128" s="8">
-        <v>0.0331</v>
-      </c>
-      <c r="H128" s="10">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E129" s="5">
-        <v>2023</v>
-      </c>
-      <c r="F129" s="7">
-        <v>0.814477540940993</v>
-      </c>
-      <c r="G129" s="9">
-        <v>0.0497781648037432</v>
-      </c>
-      <c r="H129" s="11">
-        <v>0.107859986136383</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E129" s="4">
+        <v>2022</v>
+      </c>
+      <c r="F129" s="6">
+        <v>0.8564</v>
+      </c>
+      <c r="G129" s="8">
+        <v>0.0264</v>
+      </c>
+      <c r="H129" s="10">
+        <v>0.085</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E130" s="5">
-        <v>2023</v>
-      </c>
-      <c r="F130" s="7">
-        <v>0.835462911523821</v>
-      </c>
-      <c r="G130" s="9">
-        <v>0.0500680955127466</v>
-      </c>
-      <c r="H130" s="11">
-        <v>0.110262666974276</v>
+      <c r="A130">
+        <v>5042</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E130" s="4">
+        <v>2022</v>
+      </c>
+      <c r="F130" s="6">
+        <v>0.9444</v>
+      </c>
+      <c r="G130" s="8">
+        <v>0.0502</v>
+      </c>
+      <c r="H130" s="10">
+        <v>0.1111</v>
       </c>
     </row>
     <row r="131">
@@ -4686,103 +4730,107 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E131" s="5">
+        <v>2022</v>
+      </c>
+      <c r="F131" s="7">
+        <v>0.866090839051402</v>
+      </c>
+      <c r="G131" s="9">
+        <v>0.0453423558444685</v>
+      </c>
+      <c r="H131" s="11">
+        <v>0.0978877031419285</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E132" s="5">
+        <v>2022</v>
+      </c>
+      <c r="F132" s="7">
+        <v>0.853651854751433</v>
+      </c>
+      <c r="G132" s="9">
+        <v>0.0414737755877409</v>
+      </c>
+      <c r="H132" s="11">
+        <v>0.0844889083331414</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E131" s="5">
-        <v>2023</v>
-      </c>
-      <c r="F131" s="7">
-        <v>0.918872049744332</v>
-      </c>
-      <c r="G131" s="9">
-        <v>0.0482273700759845</v>
-      </c>
-      <c r="H131" s="11">
-        <v>0.0970888092043982</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132">
-        <v>5113</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Buriticá</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E132" s="4">
-        <v>2024</v>
-      </c>
-      <c r="F132" s="6">
-        <v>0.8007</v>
-      </c>
-      <c r="G132" s="8">
-        <v>0.0801</v>
-      </c>
-      <c r="H132" s="10">
-        <v>0.0964</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133">
-        <v>5240</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Ebéjico</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E133" s="4">
-        <v>2024</v>
-      </c>
-      <c r="F133" s="6">
-        <v>0.6989</v>
-      </c>
-      <c r="G133" s="8">
-        <v>0.032</v>
-      </c>
-      <c r="H133" s="10">
-        <v>0.0761</v>
+      <c r="E133" s="5">
+        <v>2022</v>
+      </c>
+      <c r="F133" s="7">
+        <v>0.933206334367635</v>
+      </c>
+      <c r="G133" s="9">
+        <v>0.0470407053528837</v>
+      </c>
+      <c r="H133" s="11">
+        <v>0.0650811900901068</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>5306</v>
+        <v>5113</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4796,25 +4844,25 @@
         </is>
       </c>
       <c r="E134" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F134" s="6">
-        <v>0.9933</v>
+        <v>0.8024</v>
       </c>
       <c r="G134" s="8">
-        <v>0.0399</v>
+        <v>0.0689</v>
       </c>
       <c r="H134" s="10">
-        <v>0.0885</v>
+        <v>0.1224</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>5347</v>
+        <v>5240</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4828,25 +4876,25 @@
         </is>
       </c>
       <c r="E135" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F135" s="6">
-        <v>0.7856</v>
+        <v>0.6982</v>
       </c>
       <c r="G135" s="8">
-        <v>0.0493</v>
+        <v>0.0534</v>
       </c>
       <c r="H135" s="10">
-        <v>0.0704</v>
+        <v>0.1129</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>5501</v>
+        <v>5306</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Olaya</t>
+          <t>Giraldo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4860,25 +4908,25 @@
         </is>
       </c>
       <c r="E136" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F136" s="6">
-        <v>0.7642</v>
+        <v>1.0116</v>
       </c>
       <c r="G136" s="8">
-        <v>0.0249</v>
+        <v>0.0483</v>
       </c>
       <c r="H136" s="10">
-        <v>0.0934</v>
+        <v>0.1379</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>5628</v>
+        <v>5347</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4892,149 +4940,603 @@
         </is>
       </c>
       <c r="E137" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F137" s="6">
-        <v>0.7439</v>
+        <v>0.7902</v>
       </c>
       <c r="G137" s="8">
-        <v>0.0064</v>
+        <v>0.0734</v>
       </c>
       <c r="H137" s="10">
-        <v>0.0547</v>
+        <v>0.1272</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
+        <v>5501</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E138" s="4">
+        <v>2023</v>
+      </c>
+      <c r="F138" s="6">
+        <v>0.8116</v>
+      </c>
+      <c r="G138" s="8">
+        <v>0.0352</v>
+      </c>
+      <c r="H138" s="10">
+        <v>0.0938</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>5628</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E139" s="4">
+        <v>2023</v>
+      </c>
+      <c r="F139" s="6">
+        <v>0.7857</v>
+      </c>
+      <c r="G139" s="8">
+        <v>0.045</v>
+      </c>
+      <c r="H139" s="10">
+        <v>0.0911</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
         <v>5656</v>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>San Jerónimo</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E138" s="4">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E140" s="4">
+        <v>2023</v>
+      </c>
+      <c r="F140" s="6">
+        <v>0.848</v>
+      </c>
+      <c r="G140" s="8">
+        <v>0.0331</v>
+      </c>
+      <c r="H140" s="10">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>5042</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E141" s="4">
+        <v>2023</v>
+      </c>
+      <c r="F141" s="6">
+        <v>0.9433</v>
+      </c>
+      <c r="G141" s="8">
+        <v>0.0413</v>
+      </c>
+      <c r="H141" s="10">
+        <v>0.1132</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E142" s="5">
+        <v>2023</v>
+      </c>
+      <c r="F142" s="7">
+        <v>0.853542695001207</v>
+      </c>
+      <c r="G142" s="9">
+        <v>0.0472071782178218</v>
+      </c>
+      <c r="H142" s="11">
+        <v>0.109479334701763</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E143" s="5">
+        <v>2023</v>
+      </c>
+      <c r="F143" s="7">
+        <v>0.835462911523821</v>
+      </c>
+      <c r="G143" s="9">
+        <v>0.0500680955127466</v>
+      </c>
+      <c r="H143" s="11">
+        <v>0.110262666974276</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E144" s="5">
+        <v>2023</v>
+      </c>
+      <c r="F144" s="7">
+        <v>0.918872049744332</v>
+      </c>
+      <c r="G144" s="9">
+        <v>0.0482273700759845</v>
+      </c>
+      <c r="H144" s="11">
+        <v>0.0970888092043982</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>5113</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E145" s="4">
         <v>2024</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F145" s="6">
+        <v>0.8007</v>
+      </c>
+      <c r="G145" s="8">
+        <v>0.0801</v>
+      </c>
+      <c r="H145" s="10">
+        <v>0.0964</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>5240</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E146" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F146" s="6">
+        <v>0.6989</v>
+      </c>
+      <c r="G146" s="8">
+        <v>0.032</v>
+      </c>
+      <c r="H146" s="10">
+        <v>0.0761</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>5306</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E147" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F147" s="6">
+        <v>0.9933</v>
+      </c>
+      <c r="G147" s="8">
+        <v>0.0399</v>
+      </c>
+      <c r="H147" s="10">
+        <v>0.0885</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>5347</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E148" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F148" s="6">
+        <v>0.7856</v>
+      </c>
+      <c r="G148" s="8">
+        <v>0.0493</v>
+      </c>
+      <c r="H148" s="10">
+        <v>0.0704</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>5501</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E149" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F149" s="6">
+        <v>0.7642</v>
+      </c>
+      <c r="G149" s="8">
+        <v>0.0249</v>
+      </c>
+      <c r="H149" s="10">
+        <v>0.0934</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>5628</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E150" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F150" s="6">
+        <v>0.7439</v>
+      </c>
+      <c r="G150" s="8">
+        <v>0.0064</v>
+      </c>
+      <c r="H150" s="10">
+        <v>0.0547</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>5656</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E151" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F151" s="6">
         <v>0.8507</v>
       </c>
-      <c r="G138" s="8">
+      <c r="G151" s="8">
         <v>0.0741</v>
       </c>
-      <c r="H138" s="10">
+      <c r="H151" s="10">
         <v>0.0924</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
+    <row r="152">
+      <c r="A152">
+        <v>5042</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E152" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F152" s="6">
+        <v>0.8919</v>
+      </c>
+      <c r="G152" s="8">
+        <v>0.0367</v>
+      </c>
+      <c r="H152" s="10">
+        <v>0.1076</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA TURÍSTICA Y AGROECOLÓGICA (por población escolar)</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E139" s="5">
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E153" s="5">
         <v>2024</v>
       </c>
-      <c r="F139" s="7">
-        <v>0.802937376992075</v>
-      </c>
-      <c r="G139" s="9">
-        <v>0.0481529652529827</v>
-      </c>
-      <c r="H139" s="11">
-        <v>0.0816860141078116</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="F153" s="7">
+        <v>0.829912269417476</v>
+      </c>
+      <c r="G153" s="9">
+        <v>0.0446802427184466</v>
+      </c>
+      <c r="H153" s="11">
+        <v>0.0895435497572816</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población escolar)</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E140" s="5">
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E154" s="5">
         <v>2024</v>
       </c>
-      <c r="F140" s="7">
+      <c r="F154" s="7">
         <v>0.806890400555684</v>
       </c>
-      <c r="G140" s="9">
+      <c r="G154" s="9">
         <v>0.0392308798332947</v>
       </c>
-      <c r="H140" s="11">
+      <c r="H154" s="11">
         <v>0.0998673141931003</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población escolar)</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E141" s="5">
+      <c r="E155" s="5">
         <v>2024</v>
       </c>
-      <c r="F141" s="7">
+      <c r="F155" s="7">
         <v>0.898512061092923</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G155" s="9">
         <v>0.0375749880795594</v>
       </c>
-      <c r="H141" s="11">
+      <c r="H155" s="11">
         <v>0.0927142293723201</v>
       </c>
     </row>
@@ -5047,26 +5549,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>cobertura_neta</t>
         </is>
@@ -5161,6 +5663,19 @@
       </c>
       <c r="C8">
         <v>0.8507</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>0.8919</v>
       </c>
     </row>
   </sheetData>
@@ -5172,26 +5687,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>desercion</t>
         </is>
@@ -5286,6 +5801,19 @@
       </c>
       <c r="C8">
         <v>0.0741</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>0.0367</v>
       </c>
     </row>
   </sheetData>
@@ -5297,26 +5825,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>repitencia</t>
         </is>
@@ -5411,6 +5939,19 @@
       </c>
       <c r="C8">
         <v>0.0924</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9">
+        <v>0.1076</v>
       </c>
     </row>
   </sheetData>
@@ -5422,32 +5963,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Cobertura neta</t>
         </is>
@@ -5563,6 +6104,22 @@
       </c>
       <c r="D8">
         <v>0.8507</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>2024</v>
+      </c>
+      <c r="D9">
+        <v>0.8919</v>
       </c>
     </row>
   </sheetData>
